--- a/output/graficos_nacionales/plot_nacional_migracion_flujos_od_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_migracion_flujos_od_2019.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 10:06</t>
+    <t xml:space="preserve">2026-09-18 14:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_migracion_flujos_od_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_migracion_flujos_od_2019.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:08</t>
+    <t xml:space="preserve">2026-10-05 19:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
